--- a/RAG_qa.xlsx
+++ b/RAG_qa.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyeongdohun/Documents/2024_proj_openai/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hyeongdohun/Documents/2025_proj(hdh)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDEE48C-F68F-CE4B-BFE6-E0AC892904BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7251A1-77A5-2447-8F86-B3C08777933A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5958,7 +5958,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -5981,13 +5981,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -6294,7 +6308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D699"/>
+  <dimension ref="A1:G699"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="63.83203125" customWidth="1"/>
@@ -6303,7 +6317,7 @@
     <col min="4" max="4" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6316,8 +6330,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -6331,7 +6348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -6345,7 +6362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -6359,7 +6376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -6373,7 +6390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6387,7 +6404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -6401,7 +6418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -6415,7 +6432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -6429,7 +6446,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -6443,7 +6460,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -6457,7 +6474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -6471,7 +6488,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -6485,7 +6502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -6499,7 +6516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -6513,7 +6530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>18</v>
       </c>
